--- a/RoyalWoodShop_Master_Product_List_v1.xlsx
+++ b/RoyalWoodShop_Master_Product_List_v1.xlsx
@@ -48,7 +48,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Blank on 84 rows that have never had a product code — they cannot be imported until they do. Pink cells are codes used by two different products; one code has to mean one product.</t>
+          <t xml:space="preserve">Blank on 84 rows that have never had a product code — they cannot be imported until they do. PINK = this code is used by two different products; one code has to mean one product. ORANGE = you removed this row from the previous species sheet. It is back because this list is built from the full product record. Delete the row again to confirm, or leave it to keep the product.</t>
         </r>
       </text>
     </comment>
@@ -7730,7 +7730,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -7752,12 +7752,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFCE4E4"/>
-        <bgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
         <bgColor rgb="FFFCE4E4"/>
       </patternFill>
     </fill>
@@ -7811,7 +7817,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -7844,6 +7850,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7853,7 +7863,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="7">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -7873,6 +7883,14 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE4D6"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -7938,8 +7956,8 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFCE4E4"/>
+      <rgbColor rgb="FFFCE4D6"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
@@ -8762,7 +8780,7 @@
       <c r="A12" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="8" t="s">
         <v>86</v>
       </c>
       <c r="C12" s="3" t="s">
@@ -10889,7 +10907,7 @@
       <c r="A55" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B55" s="8" t="s">
         <v>291</v>
       </c>
       <c r="C55" s="3" t="s">
@@ -11034,7 +11052,7 @@
       <c r="A58" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="B58" s="8" t="s">
         <v>307</v>
       </c>
       <c r="C58" s="3" t="s">
@@ -11181,7 +11199,7 @@
       <c r="A61" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B61" s="8" t="s">
         <v>318</v>
       </c>
       <c r="C61" s="3" t="s">
@@ -11228,7 +11246,7 @@
       <c r="A62" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B62" s="8" t="s">
         <v>322</v>
       </c>
       <c r="C62" s="3" t="s">
@@ -11324,7 +11342,7 @@
       <c r="A64" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B64" s="8" t="s">
         <v>333</v>
       </c>
       <c r="C64" s="3" t="s">
@@ -11518,7 +11536,7 @@
       <c r="A68" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="B68" s="8" t="s">
         <v>352</v>
       </c>
       <c r="C68" s="3" t="s">
@@ -12067,7 +12085,7 @@
       <c r="A79" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="B79" s="8" t="s">
         <v>399</v>
       </c>
       <c r="C79" s="3" t="s">
@@ -12163,7 +12181,7 @@
       <c r="A81" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="B81" s="8" t="s">
         <v>408</v>
       </c>
       <c r="C81" s="3" t="s">
@@ -12702,7 +12720,7 @@
       <c r="A92" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="B92" s="3" t="s">
+      <c r="B92" s="8" t="s">
         <v>456</v>
       </c>
       <c r="C92" s="3" t="s">
@@ -13090,7 +13108,7 @@
       <c r="A100" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="B100" s="3" t="s">
+      <c r="B100" s="8" t="s">
         <v>494</v>
       </c>
       <c r="C100" s="3" t="s">
@@ -13845,7 +13863,7 @@
       <c r="A115" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="B115" s="3" t="s">
+      <c r="B115" s="8" t="s">
         <v>564</v>
       </c>
       <c r="C115" s="3" t="s">
@@ -13943,7 +13961,7 @@
       <c r="A117" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="B117" s="3" t="s">
+      <c r="B117" s="8" t="s">
         <v>574</v>
       </c>
       <c r="C117" s="3" t="s">
@@ -14527,7 +14545,7 @@
       <c r="A129" s="3" t="s">
         <v>631</v>
       </c>
-      <c r="B129" s="3" t="s">
+      <c r="B129" s="8" t="s">
         <v>632</v>
       </c>
       <c r="C129" s="3" t="s">
@@ -14821,7 +14839,7 @@
       <c r="A135" s="3" t="s">
         <v>655</v>
       </c>
-      <c r="B135" s="3" t="s">
+      <c r="B135" s="8" t="s">
         <v>656</v>
       </c>
       <c r="C135" s="3" t="s">
@@ -15017,7 +15035,7 @@
       <c r="A139" s="3" t="s">
         <v>673</v>
       </c>
-      <c r="B139" s="3" t="s">
+      <c r="B139" s="8" t="s">
         <v>674</v>
       </c>
       <c r="C139" s="3" t="s">
@@ -15113,7 +15131,7 @@
       <c r="A141" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="B141" s="3" t="s">
+      <c r="B141" s="8" t="s">
         <v>681</v>
       </c>
       <c r="C141" s="3" t="s">
@@ -15160,7 +15178,7 @@
       <c r="A142" s="3" t="s">
         <v>684</v>
       </c>
-      <c r="B142" s="3" t="s">
+      <c r="B142" s="8" t="s">
         <v>685</v>
       </c>
       <c r="C142" s="3" t="s">
@@ -15307,7 +15325,7 @@
       <c r="A145" s="3" t="s">
         <v>699</v>
       </c>
-      <c r="B145" s="3" t="s">
+      <c r="B145" s="8" t="s">
         <v>700</v>
       </c>
       <c r="C145" s="3" t="s">
@@ -15354,7 +15372,7 @@
       <c r="A146" s="3" t="s">
         <v>703</v>
       </c>
-      <c r="B146" s="3" t="s">
+      <c r="B146" s="8" t="s">
         <v>704</v>
       </c>
       <c r="C146" s="3" t="s">
@@ -15552,7 +15570,7 @@
       <c r="A150" s="3" t="s">
         <v>717</v>
       </c>
-      <c r="B150" s="3" t="s">
+      <c r="B150" s="8" t="s">
         <v>718</v>
       </c>
       <c r="C150" s="3" t="s">
@@ -16109,7 +16127,7 @@
       <c r="A161" s="3" t="s">
         <v>766</v>
       </c>
-      <c r="B161" s="3" t="s">
+      <c r="B161" s="8" t="s">
         <v>767</v>
       </c>
       <c r="C161" s="3" t="s">
@@ -16454,7 +16472,7 @@
       <c r="A168" s="3" t="s">
         <v>796</v>
       </c>
-      <c r="B168" s="3" t="s">
+      <c r="B168" s="8" t="s">
         <v>797</v>
       </c>
       <c r="C168" s="3" t="s">
@@ -16501,7 +16519,7 @@
       <c r="A169" s="3" t="s">
         <v>801</v>
       </c>
-      <c r="B169" s="3" t="s">
+      <c r="B169" s="8" t="s">
         <v>802</v>
       </c>
       <c r="C169" s="3" t="s">
@@ -16548,7 +16566,7 @@
       <c r="A170" s="3" t="s">
         <v>806</v>
       </c>
-      <c r="B170" s="3" t="s">
+      <c r="B170" s="8" t="s">
         <v>807</v>
       </c>
       <c r="C170" s="3" t="s">
@@ -17291,7 +17309,7 @@
       <c r="A185" s="3" t="s">
         <v>869</v>
       </c>
-      <c r="B185" s="3" t="s">
+      <c r="B185" s="8" t="s">
         <v>870</v>
       </c>
       <c r="C185" s="3" t="s">
@@ -17338,7 +17356,7 @@
       <c r="A186" s="3" t="s">
         <v>873</v>
       </c>
-      <c r="B186" s="3" t="s">
+      <c r="B186" s="8" t="s">
         <v>874</v>
       </c>
       <c r="C186" s="3" t="s">
@@ -17640,7 +17658,7 @@
       <c r="A192" s="3" t="s">
         <v>896</v>
       </c>
-      <c r="B192" s="3" t="s">
+      <c r="B192" s="8" t="s">
         <v>897</v>
       </c>
       <c r="C192" s="3" t="s">
@@ -17736,7 +17754,7 @@
       <c r="A194" s="3" t="s">
         <v>904</v>
       </c>
-      <c r="B194" s="3" t="s">
+      <c r="B194" s="8" t="s">
         <v>905</v>
       </c>
       <c r="C194" s="3" t="s">
@@ -17830,7 +17848,7 @@
       <c r="A196" s="3" t="s">
         <v>912</v>
       </c>
-      <c r="B196" s="3" t="s">
+      <c r="B196" s="8" t="s">
         <v>913</v>
       </c>
       <c r="C196" s="3" t="s">
@@ -18673,7 +18691,7 @@
       <c r="A213" s="3" t="s">
         <v>973</v>
       </c>
-      <c r="B213" s="3" t="s">
+      <c r="B213" s="8" t="s">
         <v>974</v>
       </c>
       <c r="C213" s="3" t="s">
@@ -19459,7 +19477,7 @@
       <c r="A229" s="3" t="s">
         <v>1045</v>
       </c>
-      <c r="B229" s="3" t="s">
+      <c r="B229" s="8" t="s">
         <v>1046</v>
       </c>
       <c r="C229" s="3" t="s">
@@ -19555,7 +19573,7 @@
       <c r="A231" s="3" t="s">
         <v>1054</v>
       </c>
-      <c r="B231" s="3" t="s">
+      <c r="B231" s="8" t="s">
         <v>1055</v>
       </c>
       <c r="C231" s="3" t="s">
@@ -27708,7 +27726,7 @@
       <c r="A406" s="3" t="s">
         <v>1572</v>
       </c>
-      <c r="B406" s="3" t="s">
+      <c r="B406" s="8" t="s">
         <v>1573</v>
       </c>
       <c r="C406" s="3" t="s">
@@ -27847,7 +27865,7 @@
       <c r="A409" s="3" t="s">
         <v>1587</v>
       </c>
-      <c r="B409" s="3" t="s">
+      <c r="B409" s="8" t="s">
         <v>1588</v>
       </c>
       <c r="C409" s="3" t="s">
@@ -28172,7 +28190,7 @@
       <c r="A416" s="3" t="s">
         <v>1612</v>
       </c>
-      <c r="B416" s="3" t="s">
+      <c r="B416" s="8" t="s">
         <v>1613</v>
       </c>
       <c r="C416" s="3" t="s">
@@ -29927,7 +29945,7 @@
       <c r="A455" s="3" t="s">
         <v>1779</v>
       </c>
-      <c r="B455" s="3" t="s">
+      <c r="B455" s="8" t="s">
         <v>1780</v>
       </c>
       <c r="C455" s="3" t="s">
@@ -30144,7 +30162,7 @@
       <c r="A460" s="3" t="s">
         <v>1799</v>
       </c>
-      <c r="B460" s="3" t="s">
+      <c r="B460" s="8" t="s">
         <v>1800</v>
       </c>
       <c r="C460" s="3" t="s">
@@ -30412,7 +30430,7 @@
       <c r="A466" s="3" t="s">
         <v>1819</v>
       </c>
-      <c r="B466" s="3" t="s">
+      <c r="B466" s="8" t="s">
         <v>1820</v>
       </c>
       <c r="C466" s="3" t="s">
@@ -30455,7 +30473,7 @@
       <c r="A467" s="3" t="s">
         <v>1823</v>
       </c>
-      <c r="B467" s="3" t="s">
+      <c r="B467" s="8" t="s">
         <v>1824</v>
       </c>
       <c r="C467" s="3" t="s">
@@ -30856,7 +30874,7 @@
       <c r="A476" s="3" t="s">
         <v>1858</v>
       </c>
-      <c r="B476" s="3" t="s">
+      <c r="B476" s="8" t="s">
         <v>1859</v>
       </c>
       <c r="C476" s="3" t="s">
@@ -30899,7 +30917,7 @@
       <c r="A477" s="3" t="s">
         <v>1861</v>
       </c>
-      <c r="B477" s="3" t="s">
+      <c r="B477" s="8" t="s">
         <v>1862</v>
       </c>
       <c r="C477" s="3" t="s">
@@ -31179,7 +31197,7 @@
       <c r="A483" s="3" t="s">
         <v>1887</v>
       </c>
-      <c r="B483" s="3" t="s">
+      <c r="B483" s="8" t="s">
         <v>1888</v>
       </c>
       <c r="C483" s="3" t="s">
@@ -31365,7 +31383,7 @@
       <c r="A487" s="3" t="s">
         <v>1904</v>
       </c>
-      <c r="B487" s="3" t="s">
+      <c r="B487" s="8" t="s">
         <v>1905</v>
       </c>
       <c r="C487" s="3" t="s">
@@ -32284,7 +32302,7 @@
       <c r="A508" s="3" t="s">
         <v>1965</v>
       </c>
-      <c r="B508" s="3" t="s">
+      <c r="B508" s="8" t="s">
         <v>1966</v>
       </c>
       <c r="C508" s="3" t="s">
@@ -32329,7 +32347,7 @@
       <c r="A509" s="3" t="s">
         <v>1969</v>
       </c>
-      <c r="B509" s="3" t="s">
+      <c r="B509" s="8" t="s">
         <v>1970</v>
       </c>
       <c r="C509" s="3" t="s">
@@ -32421,7 +32439,7 @@
       <c r="A511" s="3" t="s">
         <v>1977</v>
       </c>
-      <c r="B511" s="3" t="s">
+      <c r="B511" s="8" t="s">
         <v>1978</v>
       </c>
       <c r="C511" s="3" t="s">
@@ -32466,7 +32484,7 @@
       <c r="A512" s="3" t="s">
         <v>1981</v>
       </c>
-      <c r="B512" s="3" t="s">
+      <c r="B512" s="8" t="s">
         <v>1982</v>
       </c>
       <c r="C512" s="3" t="s">
@@ -32556,7 +32574,7 @@
       <c r="A514" s="3" t="s">
         <v>1987</v>
       </c>
-      <c r="B514" s="3" t="s">
+      <c r="B514" s="8" t="s">
         <v>1988</v>
       </c>
       <c r="C514" s="3" t="s">
@@ -32601,7 +32619,7 @@
       <c r="A515" s="3" t="s">
         <v>1991</v>
       </c>
-      <c r="B515" s="3" t="s">
+      <c r="B515" s="8" t="s">
         <v>1992</v>
       </c>
       <c r="C515" s="3" t="s">
@@ -32693,7 +32711,7 @@
       <c r="A517" s="3" t="s">
         <v>1999</v>
       </c>
-      <c r="B517" s="3" t="s">
+      <c r="B517" s="8" t="s">
         <v>2000</v>
       </c>
       <c r="C517" s="3" t="s">
@@ -32738,7 +32756,7 @@
       <c r="A518" s="3" t="s">
         <v>2003</v>
       </c>
-      <c r="B518" s="3" t="s">
+      <c r="B518" s="8" t="s">
         <v>2004</v>
       </c>
       <c r="C518" s="3" t="s">
@@ -32783,7 +32801,7 @@
       <c r="A519" s="3" t="s">
         <v>2007</v>
       </c>
-      <c r="B519" s="3" t="s">
+      <c r="B519" s="8" t="s">
         <v>2008</v>
       </c>
       <c r="C519" s="3" t="s">
@@ -43884,7 +43902,7 @@
     </row>
     <row r="786" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A786" s="3"/>
-      <c r="B786" s="3" t="s">
+      <c r="B786" s="8" t="s">
         <v>2426</v>
       </c>
       <c r="C786" s="5"/>
@@ -43925,7 +43943,7 @@
     </row>
     <row r="787" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A787" s="3"/>
-      <c r="B787" s="3" t="s">
+      <c r="B787" s="8" t="s">
         <v>2427</v>
       </c>
       <c r="C787" s="5"/>
@@ -43966,7 +43984,7 @@
     </row>
     <row r="788" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A788" s="3"/>
-      <c r="B788" s="3" t="s">
+      <c r="B788" s="8" t="s">
         <v>2428</v>
       </c>
       <c r="C788" s="5"/>
@@ -44007,7 +44025,7 @@
     </row>
     <row r="789" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A789" s="3"/>
-      <c r="B789" s="3" t="s">
+      <c r="B789" s="8" t="s">
         <v>2429</v>
       </c>
       <c r="C789" s="5"/>
@@ -44048,7 +44066,7 @@
     </row>
     <row r="790" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A790" s="3"/>
-      <c r="B790" s="3" t="s">
+      <c r="B790" s="8" t="s">
         <v>2430</v>
       </c>
       <c r="C790" s="5"/>
@@ -44089,7 +44107,7 @@
     </row>
     <row r="791" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A791" s="3"/>
-      <c r="B791" s="3" t="s">
+      <c r="B791" s="8" t="s">
         <v>2431</v>
       </c>
       <c r="C791" s="5"/>
@@ -44130,7 +44148,7 @@
     </row>
     <row r="792" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A792" s="3"/>
-      <c r="B792" s="3" t="s">
+      <c r="B792" s="8" t="s">
         <v>2432</v>
       </c>
       <c r="C792" s="5"/>
@@ -46458,7 +46476,7 @@
     </row>
     <row r="846" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A846" s="3"/>
-      <c r="B846" s="3" t="s">
+      <c r="B846" s="8" t="s">
         <v>2495</v>
       </c>
       <c r="C846" s="5"/>
@@ -47039,7 +47057,7 @@
     </row>
     <row r="859" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A859" s="3"/>
-      <c r="B859" s="3" t="s">
+      <c r="B859" s="8" t="s">
         <v>2512</v>
       </c>
       <c r="C859" s="5"/>

--- a/RoyalWoodShop_Master_Product_List_v1.xlsx
+++ b/RoyalWoodShop_Master_Product_List_v1.xlsx
@@ -48,7 +48,962 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Blank on 84 rows that have never had a product code — they cannot be imported until they do. PINK = this code is used by two different products; one code has to mean one product. ORANGE = you removed this row from the previous species sheet. It is back because this list is built from the full product record. Delete the row again to confirm, or leave it to keep the product.</t>
+          <t xml:space="preserve">Blank on 84 rows that have never had a product code — they cannot be imported until they do.
+SALMON = this code is used by two different products. Something to fix.
+BLUE = you removed this row from the previous species sheet. For information.
+Hover any shaded cell and it tells you which it is and what to do.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B2" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">SALMON — this product code is on two rows for two different products.
+The import matches on code, so it cannot tell them apart: only the first row is imported and the second product gets nothing.
+Fix it by giving one of them its own code, or by deleting one row if they are the same product recorded twice.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B55" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B58" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B61" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B62" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B64" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B68" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B79" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B81" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B92" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B100" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B115" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B117" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B129" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B135" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B139" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B141" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B142" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B145" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B146" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B150" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B161" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B168" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B169" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B170" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B185" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B186" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B192" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B194" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B196" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B197" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">SALMON — this product code is on two rows for two different products.
+The import matches on code, so it cannot tell them apart: only the first row is imported and the second product gets nothing.
+Fix it by giving one of them its own code, or by deleting one row if they are the same product recorded twice.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B213" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B229" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B231" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B406" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B409" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B416" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B425" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">SALMON — this product code is on two rows for two different products.
+The import matches on code, so it cannot tell them apart: only the first row is imported and the second product gets nothing.
+Fix it by giving one of them its own code, or by deleting one row if they are the same product recorded twice.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B426" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">SALMON — this product code is on two rows for two different products.
+The import matches on code, so it cannot tell them apart: only the first row is imported and the second product gets nothing.
+Fix it by giving one of them its own code, or by deleting one row if they are the same product recorded twice.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B455" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B460" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B462" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">SALMON — this product code is on two rows for two different products.
+The import matches on code, so it cannot tell them apart: only the first row is imported and the second product gets nothing.
+Fix it by giving one of them its own code, or by deleting one row if they are the same product recorded twice.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B463" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">SALMON — this product code is on two rows for two different products.
+The import matches on code, so it cannot tell them apart: only the first row is imported and the second product gets nothing.
+Fix it by giving one of them its own code, or by deleting one row if they are the same product recorded twice.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B466" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B467" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B476" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B477" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B483" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B487" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B508" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B509" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B511" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B512" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B514" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B515" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B517" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B518" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B519" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B786" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B787" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B788" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B789" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B790" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B791" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B792" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B846" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B859" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BLUE — you deleted this row from the previous species sheet.
+It is back because this list is built from the full product record, which never saw that deletion. Nothing is wrong with the row.
+Delete it again if the product is discontinued, or leave it to keep the product.</t>
         </r>
       </text>
     </comment>
@@ -7746,25 +8701,25 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF7C7AC"/>
-        <bgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFF8CBAD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4E4"/>
-        <bgColor rgb="FFFCE4D6"/>
+        <fgColor rgb="FFF8CBAD"/>
+        <bgColor rgb="FFF7C7AC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFCE4D6"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4D6"/>
-        <bgColor rgb="FFFCE4E4"/>
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -7890,7 +8845,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFCE4D6"/>
+          <fgColor rgb="FFDDEBF7"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -7898,7 +8853,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFCE4E4"/>
+          <fgColor rgb="FFF8CBAD"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -7936,12 +8891,12 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FFF7C7AC"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFF2CC"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFDDEBF7"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -7956,12 +8911,12 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFFCE4E4"/>
-      <rgbColor rgb="FFFCE4D6"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFF7C7AC"/>
+      <rgbColor rgb="FFF8CBAD"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>

--- a/RoyalWoodShop_Master_Product_List_v1.xlsx
+++ b/RoyalWoodShop_Master_Product_List_v1.xlsx
@@ -1007,6 +1007,21 @@
         </r>
       </text>
     </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">A product can sit in more than one category — separate them with a pipe. Category and sub-category pair up BY POSITION:
+    Category      TRIM &amp; MOULDINGS|SHEET GOODS
+    type/sub-cat  Decorative|Sheet Panels
+The FIRST category is the one the product’s web address uses, and that does not change when you add a second. Never add a second row for the same product.</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E1" authorId="0">
       <text>
         <r>
@@ -1015,7 +1030,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">A product can sit under more than one — separate them with a pipe, the same way the species column does it: Backband|Base Cap. Do NOT add a second row for the same product; one code has to mean one product.</t>
+          <t xml:space="preserve">One per category, in the same order — see the Category note. Several sub-categories under a single category also work: Backband|Base Cap.</t>
         </r>
       </text>
     </comment>
